--- a/public/descargas/plantilla-roi-automatizacion.xlsx
+++ b/public/descargas/plantilla-roi-automatizacion.xlsx
@@ -44,12 +44,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="85">
   <si>
     <t xml:space="preserve">Plantilla de ROI de automatización</t>
   </si>
   <si>
-    <t xml:space="preserve">ANVAR TECH · IA &amp; Automatización · ia.anvartech.cl · Versión 1.0 (25/09/2026)</t>
+    <t xml:space="preserve">ANVAR TECH · IA &amp; Automatización · ia.anvartech.cl · Versión 1.1 (25/09/2026)</t>
   </si>
   <si>
     <t xml:space="preserve">Ingresa tus datos en las celdas amarillas (texto azul). Todo lo demás se calcula solo. Los valores que trae son un ejemplo.</t>
@@ -91,6 +91,12 @@
     <t xml:space="preserve">Sueldo bruto más aportes del empleador, dividido por las horas trabajadas al mes. Lo tiene quien hace las remuneraciones.</t>
   </si>
   <si>
+    <t xml:space="preserve">Horas a la semana por persona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veces por semana × minutos ÷ 60. Es el dato "Horas a la semana, cada una" de la calculadora en línea.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2. La automatización</t>
   </si>
   <si>
@@ -100,79 +106,85 @@
     <t xml:space="preserve">Si no sabes, deja 60%. El resto queda para revisión humana y excepciones.</t>
   </si>
   <si>
-    <t xml:space="preserve">Costo de implementación ($, neto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo que cuesta dejarla funcionando. Ejemplo: piloto desde UF 40 + IVA (con UF de $41.000). Una Automatización Express parte en $199.900 + IVA.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Costo mensual de mantención y licencias ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soporte, suscripciones o licencias que necesite. 0 si no hay.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Resultados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horas al año que hoy toma el proceso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personas × veces por semana × minutos ÷ 60 × semanas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Costo anual del proceso hoy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horas al año × costo por hora.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horas que se liberan al año</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horas al año × parte automatizable.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horas liberadas por persona a la semana</t>
+    <t xml:space="preserve">Inversión inicial ($, neto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tu cotización real, si la tienes. El ejemplo es un piloto desde UF 40 + IVA con UF de $41.000 (24/09/2026); una Automatización Express parte en $199.900 + IVA. Actualiza con la UF del día.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costo mensual de operación o soporte ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licencias, suscripciones o soporte. 0 si no hay.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Resultados (mismas fórmulas que la calculadora en línea)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horas manuales al año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personas × horas a la semana × semanas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costo anual actual del proceso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horas manuales × costo por hora.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horas potencialmente recuperadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horas manuales × parte automatizable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horas recuperadas por persona a la semana</t>
   </si>
   <si>
     <t xml:space="preserve">Para explicarlo al equipo: cuánto tiempo recupera cada persona.</t>
   </si>
   <si>
-    <t xml:space="preserve">Ahorro bruto anual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor del tiempo liberado.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Costo anual de mantención</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mantención mensual × 12.</t>
+    <t xml:space="preserve">Ahorro bruto anual estimado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor del tiempo recuperado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costos recurrentes al año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costo mensual × 12.</t>
   </si>
   <si>
     <t xml:space="preserve">Ahorro neto anual</t>
   </si>
   <si>
-    <t xml:space="preserve">Ahorro bruto menos mantención.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payback (meses para recuperar la inversión)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implementación ÷ ahorro neto mensual.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROI a 1 año</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(Ahorro neto del primer año − implementación) ÷ implementación.</t>
+    <t xml:space="preserve">Ahorro bruto menos costos recurrentes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahorro neto estimado, año 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahorro neto anual menos la inversión inicial.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payback estimado (meses)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inversión ÷ ahorro neto mensual. "Sin recuperación" si los costos recurrentes igualan o superan el ahorro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROI año 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahorro neto del año 1 ÷ inversión.</t>
   </si>
   <si>
     <t xml:space="preserve">ROI a 3 años</t>
   </si>
   <si>
-    <t xml:space="preserve">(Ahorro neto de tres años − implementación) ÷ implementación.</t>
+    <t xml:space="preserve">(Ahorro neto anual × 3 − inversión) ÷ inversión.</t>
   </si>
   <si>
     <t xml:space="preserve">Estimación referencial basada en los datos ingresados. El resultado real depende del proceso, la implementación y el contexto operacional. No incluye el costo de errores, reprocesos ni atrasos, que suele ser mayor que el de las horas.</t>
@@ -298,9 +310,9 @@
     <numFmt numFmtId="165" formatCode="0"/>
     <numFmt numFmtId="166" formatCode="0&quot; min&quot;"/>
     <numFmt numFmtId="167" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
-    <numFmt numFmtId="168" formatCode="0.0%;\(0.0%\);\-"/>
-    <numFmt numFmtId="169" formatCode="#,##0&quot; h&quot;;\(#,##0&quot; h)&quot;;\-"/>
-    <numFmt numFmtId="170" formatCode="0.0&quot; h&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.0&quot; h&quot;"/>
+    <numFmt numFmtId="169" formatCode="0.0%;\(0.0%\);\-"/>
+    <numFmt numFmtId="170" formatCode="#,##0&quot; h&quot;;\(#,##0&quot; h)&quot;;\-"/>
     <numFmt numFmtId="171" formatCode="0.0&quot; meses&quot;"/>
   </numFmts>
   <fonts count="12">
@@ -500,7 +512,35 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -508,34 +548,6 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -564,11 +576,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -576,7 +588,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -848,7 +860,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
@@ -935,67 +947,67 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="3" t="s">
+      <c r="B11" s="10" t="n">
+        <f aca="false">B7*B8/60</f>
+        <v>6</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="9" t="n">
-        <v>1640000</v>
+      <c r="B14" s="11" t="n">
+        <v>0.6</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0</v>
+        <v>1640000</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="3" t="s">
+      <c r="B16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="3" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="11" t="n">
-        <f aca="false">B6*B7*B8/60*B9</f>
-        <v>1320</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1003,32 +1015,32 @@
         <v>25</v>
       </c>
       <c r="B19" s="12" t="n">
-        <f aca="false">B18*B10</f>
-        <v>11880000</v>
+        <f aca="false">B6*B11*B9</f>
+        <v>1320</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="14" t="n">
-        <f aca="false">B18*B13</f>
-        <v>792</v>
+      <c r="B20" s="13" t="n">
+        <f aca="false">B19*B10</f>
+        <v>11880000</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="14" t="s">
         <v>29</v>
       </c>
       <c r="B21" s="15" t="n">
-        <f aca="false">IF(B6*B9&gt;0,B20/B6/B9,0)</f>
-        <v>3.6</v>
+        <f aca="false">B19*B14</f>
+        <v>792</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>30</v>
@@ -1038,9 +1050,9 @@
       <c r="A22" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="12" t="n">
-        <f aca="false">B20*B10</f>
-        <v>7128000</v>
+      <c r="B22" s="10" t="n">
+        <f aca="false">IF(B6*B9&gt;0,B21/B6/B9,0)</f>
+        <v>3.6</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>32</v>
@@ -1050,103 +1062,127 @@
       <c r="A23" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="12" t="n">
-        <f aca="false">B15*12</f>
-        <v>0</v>
+      <c r="B23" s="13" t="n">
+        <f aca="false">B21*B10</f>
+        <v>7128000</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B24" s="16" t="n">
-        <f aca="false">B22-B23</f>
-        <v>7128000</v>
+      <c r="B24" s="13" t="n">
+        <f aca="false">B16*12</f>
+        <v>0</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="17" t="n">
-        <f aca="false">IF(B24&gt;0,B14/(B24/12),"No se recupera")</f>
-        <v>2.76094276094276</v>
+      <c r="B25" s="13" t="n">
+        <f aca="false">B23-B24</f>
+        <v>7128000</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="18" t="n">
-        <f aca="false">IF(B14&gt;0,(B24-B14)/B14,0)</f>
-        <v>3.34634146341463</v>
+      <c r="B26" s="16" t="n">
+        <f aca="false">B25-B15</f>
+        <v>5488000</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="18" t="n">
-        <f aca="false">IF(B14&gt;0,(B24*3-B14)/B14,0)</f>
-        <v>12.0390243902439</v>
+      <c r="B27" s="17" t="n">
+        <f aca="false">IF(B23&lt;=0,"No aplica",IF(B25&lt;=0,"Sin recuperación",IF(B15&lt;=0,"No aplica",B15/(B25/12))))</f>
+        <v>2.76094276094276</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="20" t="s">
+      <c r="B28" s="18" t="n">
+        <f aca="false">IF(B15&gt;0,B26/B15,"No aplica")</f>
+        <v>3.34634146341463</v>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B32" s="21" t="s">
+      <c r="B29" s="18" t="n">
+        <f aca="false">IF(B15&gt;0,(B25*3-B15)/B15,"No aplica")</f>
+        <v>12.0390243902439</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>46</v>
       </c>
     </row>
+    <row r="31" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+    </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B33" s="22"/>
+      <c r="A33" s="20" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
-        <v>48</v>
+      <c r="A34" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="21" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" s="22"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A31:C31"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="false" error="Ingresa un porcentaje entre 0% y 100%." errorStyle="stop" errorTitle="Porcentaje" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B13" type="decimal">
+    <dataValidation allowBlank="false" error="Ingresa un porcentaje entre 0% y 100%." errorStyle="stop" errorTitle="Porcentaje" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B14" type="decimal">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Ingresa un número mayor o igual a 0." errorStyle="stop" errorTitle="Valor" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B6:B10 B14:B15" type="decimal">
+    <dataValidation allowBlank="false" error="Ingresa un número mayor o igual a 0." errorStyle="stop" errorTitle="Valor" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B6:B10 B15:B16" type="decimal">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1183,49 +1219,49 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J4" s="23" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B5" s="24" t="n">
         <v>3</v>
@@ -1477,7 +1513,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="20" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G16" s="29" t="n">
         <f aca="false">SUM(G5:G14)</f>
@@ -1498,7 +1534,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1525,7 +1561,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="31" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1533,22 +1569,22 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="32" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="32" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="32" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1556,22 +1592,22 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="33" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="32" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1579,12 +1615,12 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="32" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1592,12 +1628,12 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="33" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="32" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1605,22 +1641,22 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/public/descargas/plantilla-roi-automatizacion.xlsx
+++ b/public/descargas/plantilla-roi-automatizacion.xlsx
@@ -109,7 +109,7 @@
     <t xml:space="preserve">Inversión inicial ($, neto)</t>
   </si>
   <si>
-    <t xml:space="preserve">Tu cotización real, si la tienes. El ejemplo es un piloto desde UF 40 + IVA con UF de $41.000 (24/09/2026); una Automatización Express parte en $199.900 + IVA. Actualiza con la UF del día.</t>
+    <t xml:space="preserve">Tu cotización real, si la tienes. El ejemplo usa $1.640.000. Como referencia, un piloto parte en UF 40 + IVA (pásalo a pesos con la UF del día) y una Automatización Express en $199.900 + IVA.</t>
   </si>
   <si>
     <t xml:space="preserve">Costo mensual de operación o soporte ($)</t>
@@ -979,7 +979,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
         <v>20</v>
       </c>
